--- a/10_Pjt_Hierarchy/계층게시판.xlsx
+++ b/10_Pjt_Hierarchy/계층게시판.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GDJ\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GDJ61\springstudy\10_Pjt_Hierarchy\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13590"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24210" windowHeight="9525"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,15 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>1. 원글 삽입하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 답글 달기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="51">
   <si>
     <t>DEPTH</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,6 +39,200 @@
   </si>
   <si>
     <t>GROUP_ORDER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 원글 달기(부모)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 답글 달기(자식)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원글 DEPTH + 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BBS_NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEPTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROUP_NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROUP_ORDER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 점심은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원글의 GROUP_ORDER + 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ㄴ삼겹살1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ㄴ돼지불백2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ㄴ돼지주물럭3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  ㄴ대패삼겹살4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    ㄴ저도이거요1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원글의 GROUP_NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    ㄴ난시른데요2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-&gt;2-&gt;3-&gt;4-&gt;5-&gt;6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-&gt;5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 GROUP_NO를 가진 게시글 중 원글의 GROUP_ORDER보다 큰 GROUP_ORDER를 가진 게시글의 GROUP_ORDER를 1씩 증가시킨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존 답글에
+추가 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차 정렬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROUP_NO DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 정렬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROUP_ORDER ASC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최신글이 항상 위로 올라오는 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정렬
+이전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정렬
+이후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INSERT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPDATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>답글 달기
+서비스에
+@Transactional
+추가하기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -54,7 +240,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +253,23 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -114,7 +317,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -126,6 +329,30 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -407,49 +634,419 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="15.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="10"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="10"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G12:G19"/>
+    <mergeCell ref="G25:G32"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D10"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/10_Pjt_Hierarchy/계층게시판.xlsx
+++ b/10_Pjt_Hierarchy/계층게시판.xlsx
@@ -642,7 +642,8 @@
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="15.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="1.5" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1049,6 +1050,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>